--- a/reports/二级子公司C_利润表_2025-08.xlsx
+++ b/reports/二级子公司C_利润表_2025-08.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>98257415</v>
+        <v>101476437</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>95394080</v>
+        <v>96405324</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>689639194</v>
+        <v>690234703</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>450640</v>
+        <v>445338</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3225492</v>
+        <v>3222639</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>393926</v>
+        <v>389742</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2822253</v>
+        <v>2819685</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>337032</v>
+        <v>334466</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2418839</v>
+        <v>2416963</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>313815</v>
+        <v>312796</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2257225</v>
+        <v>2256089</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>167694</v>
+        <v>167981</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1208994</v>
+        <v>1208822</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>133862</v>
+        <v>134717</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>967013</v>
+        <v>967246</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>96460446</v>
+        <v>99691397</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>93597111</v>
+        <v>94620284</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>89110863</v>
+        <v>90134882</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>644501877</v>
+        <v>645094512</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1338681</v>
+        <v>1350985</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>9668155</v>
+        <v>9676398</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>894423</v>
+        <v>899145</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6446307</v>
+        <v>6450400</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3362513</v>
+        <v>3364051</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>24178026</v>
+        <v>24185437</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>449399</v>
+        <v>447413</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>3224366</v>
+        <v>3224121</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>337663</v>
+        <v>334791</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2418700</v>
+        <v>2417621</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>563307</v>
+        <v>557060</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4031668</v>
+        <v>4028701</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>675912</v>
+        <v>667982</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4838250</v>
+        <v>4833911</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2813196</v>
+        <v>2784162</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>20158769</v>
+        <v>20140613</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>50139</v>
+        <v>49783</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>400054</v>
+        <v>399896</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1340968</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>9669144</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>896200</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6447215</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>66487376</v>
+        <v>72068548</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>59228083</v>
+        <v>59929136</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>57891220</v>
+        <v>58577171</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>418930234</v>
+        <v>419284790</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1336863</v>
+        <v>1351965</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>9667568</v>
+        <v>9676460</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2251246</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>16127224</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>719116</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5160237</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>448391</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3224649</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>536719</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3868843</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>401643</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2901075</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>267347</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1933740</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>222656</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1611289</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1012533</v>
+        <v>1002421</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>7257084</v>
+        <v>7250634</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>785938</v>
+        <v>780787</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5643746</v>
+        <v>5639716</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>672008</v>
+        <v>670696</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4836673</v>
+        <v>4834671</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>5027651</v>
+        <v>5042820</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>36267983</v>
+        <v>36266514</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>199104</v>
+        <v>224663</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1599394</v>
+        <v>1612160</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>347997</v>
+        <v>351694</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2798767</v>
+        <v>2801117</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>397617</v>
+        <v>351694</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3198640</v>
+        <v>2801117</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>49743</v>
+        <v>50293</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>399866</v>
+        <v>400164</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>180869</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1440439</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>393153</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2821956</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>120065</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>959963</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>89824</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>719843</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>149383</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1199571</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>556896</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4028556</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>79520</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>639723</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>59676</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>479827</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>99615</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>799824</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>69887</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>559977</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>50045</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>400057</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40130</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>320097</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30151</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>240099</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>29973070</v>
+        <v>28952485</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>34970092</v>
+        <v>32702159</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>225035</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1612695</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>50132</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>400047</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>80139</v>
+        <v>80016</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>640130</v>
+        <v>639959</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>29892931</v>
+        <v>29097504</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2815258</v>
+        <v>2787812</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>22409624</v>
+        <v>22391689</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>27077673</v>
+        <v>26309692</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>27077673</v>
+        <v>26309692</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>27077673</v>
+        <v>26309692</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>27077673</v>
+        <v>26309692</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>27077673</v>
+        <v>26309692</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
